--- a/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260717.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260717.xlsx
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>6890</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>裕民</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>38,623,000</t>
+          <t>13,440,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2597</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>潤弘</t>
+          <t>裕民</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>14,250,000</t>
+          <t>38,623,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>6890</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>潤弘</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>13,440,000</t>
+          <t>14,250,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
